--- a/files/LOG_SLA_Master.xlsx
+++ b/files/LOG_SLA_Master.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,26 +26,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,10 +59,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,22 +77,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,17 +477,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>LOG SLA Master</t>
@@ -467,111 +501,1565 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LOG_SLA_Master.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: LOG_SLA_Master.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FY2026 Plan</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Raised</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (RM m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CAGR ~9%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ITM-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Vendor onboarding delay — Tier 1 supplier</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Pending external review</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (RM m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>412</v>
-      </c>
-      <c r="C6" t="n">
-        <v>455</v>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Margin lift</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ITM-002</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Capex business case approval pending</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Above peer median</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ITM-003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Renewal of MSA — top 5 client</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ITM-004</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S/4HANA cut-over readiness gap</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Note: placeholder demo data — not real Zava figures.</t>
+          <t>ITM-005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Talent retention plan — top-200 roles</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ITM-006</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>ESG disclosure — Scope 3 data quality</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Pending external review</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ITM-007</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Cyber-resilience tabletop exercise</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ITM-008</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Customer NPS recovery action</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ITM-009</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Working-capital DSO improvement</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ITM-010</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Treasury hedge programme reset</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ITM-011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Board-paper template refresh</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ITM-012</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Whistleblowing case — investigation</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ITM-013</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Inventory ABC re-segmentation</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Pending external review</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ITM-014</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Procurement category sourcing wave</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ITM-015</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Marketing campaign post-mortem</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>On track</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ITM-016</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>IR investor day — readiness</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ITM-017</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Internal-audit annual plan refresh</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ITM-018</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>ITGC remediation — access certification</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ITM-019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Health &amp; Safety incident review</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>ITM-020</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Data-quality master-data programme</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ITM-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Operating model — shared services design</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Re-baselined this week</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ITM-022</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Legal — contract repository migration</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Pending external review</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ITM-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Group strategy — refresh cadence</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Pending external review</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ITM-024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>M&amp;A pipeline triage</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ITM-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Lender refinancing — Tranche A</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Pending external review</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ITM-026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Tax compliance — transfer pricing</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ITM-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability assurance scoping</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ITM-028</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Customer-experience journey map refresh</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>On track</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ITM-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Insurance renewal — directors &amp; officers</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>ITM-030</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Risk appetite statement — refresh</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Daichi Maruyama</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting input from sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ITM-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>AI use-case prioritisation</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Dependency cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>ITM-032</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Procurement payment-terms harmonisation</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>On track</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
